--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/ARKANSAS_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/ARKANSAS_2016.xlsx
@@ -679,7 +679,7 @@
         <v>5</v>
       </c>
       <c r="D18">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="19">
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="24">
@@ -1399,7 +1399,7 @@
         <v>5</v>
       </c>
       <c r="D58">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="59">
@@ -1561,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="68">
@@ -1597,7 +1597,7 @@
         <v>5</v>
       </c>
       <c r="D69">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="70">
@@ -1687,7 +1687,7 @@
         <v>5</v>
       </c>
       <c r="D74">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="75">
@@ -2155,7 +2155,7 @@
         <v>5</v>
       </c>
       <c r="D100">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="101">
@@ -2227,7 +2227,7 @@
         <v>5</v>
       </c>
       <c r="D104">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="105">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C130">
@@ -2713,7 +2713,7 @@
         <v>5</v>
       </c>
       <c r="D131">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="132">
@@ -2749,7 +2749,7 @@
         <v>5</v>
       </c>
       <c r="D133">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="134">
@@ -3037,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="D149">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="150">
@@ -3181,7 +3181,7 @@
         <v>5</v>
       </c>
       <c r="D157">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="158">
@@ -3325,7 +3325,7 @@
         <v>5</v>
       </c>
       <c r="D165">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="166">
@@ -3991,7 +3991,7 @@
         <v>5</v>
       </c>
       <c r="D202">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="203">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C221">
@@ -4477,7 +4477,7 @@
         <v>5</v>
       </c>
       <c r="D229">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="230">
@@ -4729,7 +4729,7 @@
         <v>5</v>
       </c>
       <c r="D243">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="244">
@@ -4909,7 +4909,7 @@
         <v>5</v>
       </c>
       <c r="D253">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="254">
@@ -5035,7 +5035,7 @@
         <v>5</v>
       </c>
       <c r="D260">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="261">
@@ -5449,7 +5449,7 @@
         <v>5</v>
       </c>
       <c r="D283">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="284">
@@ -5485,7 +5485,7 @@
         <v>5</v>
       </c>
       <c r="D285">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="286">
@@ -5611,7 +5611,7 @@
         <v>5</v>
       </c>
       <c r="D292">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="293">
@@ -5953,7 +5953,7 @@
         <v>5</v>
       </c>
       <c r="D311">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="312">
@@ -5971,7 +5971,7 @@
         <v>5</v>
       </c>
       <c r="D312">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="313">
@@ -6097,7 +6097,7 @@
         <v>5</v>
       </c>
       <c r="D319">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="320">
@@ -7699,7 +7699,7 @@
         <v>5</v>
       </c>
       <c r="D408">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="409">
@@ -7735,7 +7735,7 @@
         <v>5</v>
       </c>
       <c r="D410">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="411">
@@ -8005,7 +8005,7 @@
         <v>5</v>
       </c>
       <c r="D425">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="426">
@@ -8455,7 +8455,7 @@
         <v>5</v>
       </c>
       <c r="D450">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="451">
@@ -8797,7 +8797,7 @@
         <v>5</v>
       </c>
       <c r="D469">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="470">
@@ -9211,7 +9211,7 @@
         <v>5</v>
       </c>
       <c r="D492">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="493">
@@ -9337,7 +9337,7 @@
         <v>5</v>
       </c>
       <c r="D499">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="500">
@@ -9913,7 +9913,7 @@
         <v>5</v>
       </c>
       <c r="D531">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="532">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C535">
@@ -10255,7 +10255,7 @@
         <v>5</v>
       </c>
       <c r="D550">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="551">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C555">
@@ -11443,7 +11443,7 @@
         <v>5</v>
       </c>
       <c r="D616">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="617">
@@ -12361,7 +12361,7 @@
         <v>5</v>
       </c>
       <c r="D667">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="668">
@@ -12379,7 +12379,7 @@
         <v>5</v>
       </c>
       <c r="D668">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="669">
@@ -12919,7 +12919,7 @@
         <v>5</v>
       </c>
       <c r="D698">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="699">
@@ -13063,7 +13063,7 @@
         <v>5</v>
       </c>
       <c r="D706">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="707">
@@ -13837,7 +13837,7 @@
         <v>5</v>
       </c>
       <c r="D749">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="750">
@@ -14053,7 +14053,7 @@
         <v>5</v>
       </c>
       <c r="D761">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="762">
@@ -14287,7 +14287,7 @@
         <v>5</v>
       </c>
       <c r="D774">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="775">
@@ -14809,7 +14809,7 @@
         <v>5</v>
       </c>
       <c r="D803">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="804">
@@ -15097,7 +15097,7 @@
         <v>5</v>
       </c>
       <c r="D819">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="820">
@@ -15259,7 +15259,7 @@
         <v>5</v>
       </c>
       <c r="D828">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="829">
@@ -15565,7 +15565,7 @@
         <v>5</v>
       </c>
       <c r="D845">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="846">
@@ -15925,7 +15925,7 @@
         <v>5</v>
       </c>
       <c r="D865">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="866">
@@ -16285,7 +16285,7 @@
         <v>5</v>
       </c>
       <c r="D885">
-        <v>0.0009584052137243627</v>
+        <v>0.0009584052137243628</v>
       </c>
     </row>
     <row r="886">
